--- a/uploads/training_data.xlsx
+++ b/uploads/training_data.xlsx
@@ -1,54 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\u01\workspace\No.1-SQL-Assist\uploads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6773BD-FB1C-472C-9B27-CFA6A0B48DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="training_data" sheetId="1" r:id="rId1"/>
+    <sheet name="training_data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>CATEGORY</t>
-  </si>
-  <si>
-    <t>TEXT</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -63,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -387,28 +420,627 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CATEGORY</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>部門関連</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>部門テーブルのすべての部門名と場所をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>部門関連</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>東京にある部門をすべて教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>部門関連</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>部門の作成日が最新の部門は何ですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>部門関連</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>部門IDが10から50までの部門名を昇順で表示してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>部門関連</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>各場所にある部門の数を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>部門関連</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>大阪にある部門の名前は何ですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>部門関連</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>部門IDが偶数の部門をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>部門関連</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>作成日が2025年以降の部門はありますか？（注: データはすべてデフォルトでSYSDATEなので、条件なしで全件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>部門関連</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>部門名のアルファベット順で最初の部門は何ですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>部門関連</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>各部門のIDと名前をIDの昇順で表示してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>社員関連</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>社員テーブルのすべての社員名と給与をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>社員関連</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>给与が500000円以上の社員を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>社員関連</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>開発部門（DEPARTMENT_ID=50）に所属する社員の名前をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>社員関連</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>入社日が2025年以降の社員は何人いますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>社員関連</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>社員の平均給与を計算してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>社員関連</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>メールアドレスが@example.comで終わる社員の名前を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>社員関連</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>给与が最も高い社員の名前と給与は何ですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>社員関連</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>部門IDが20の社員の数を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>社員関連</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>社員IDが奇数の社員の名前をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>社員関連</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>入社日が最も古い社員の名前は何ですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>プロジェクト関連</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>プロジェクトテーブルのすべてのプロジェクト名と予算をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>プロジェクト関連</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>予算が1000万円以上のプロジェクトを教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>プロジェクト関連</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>開発部門（DEPARTMENT_ID=50）が担当するプロジェクトの名前をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>プロジェクト関連</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>開始日が2025年4月以降のプロジェクトは何ですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>プロジェクト関連</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>プロジェクトの平均予算を計算してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>プロジェクト関連</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>プロジェクトIDが100以上のプロジェクトの名前を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>プロジェクト関連</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>予算が最も低いプロジェクトの名前と予算は何ですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>プロジェクト関連</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>部門IDが40のプロジェクトの数を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>プロジェクト関連</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>プロジェクト名のアルファベット順で最初のプロジェクトは何ですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>プロジェクト関連</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>開始日が2025年1月のプロジェクトをリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>社員と部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>V_EMP_DEPTビューを使って、すべての社員名と所属部門名をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>社員と部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>東京にある部門の社員の名前と給与を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>社員と部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>各部門の平均給与を計算してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>社員と部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>给与が550000円以上の社員とその部門名をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>社員と部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>開発部門の社員の名前を昇順で表示してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>社員と部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>各場所の社員数を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>社員と部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>给与が最も高い社員の名前と部門名は何ですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>社員と部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>大阪にある部門の社員の平均給与を計算してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>社員と部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>社員名が「佐藤」で始まる社員の部門名を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>社員と部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>各部門の社員数を部門名順で表示してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>プロジェクトと部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>V_DEPT_PROJECTビューを使って、すべてのプロジェクト名と担当部門名をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>プロジェクトと部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>開発部門が担当するプロジェクトの名前と予算を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>プロジェクトと部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>各部門のプロジェクト数を計算してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>プロジェクトと部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>予算が5000万円以上のプロジェクトとその部門名をリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>プロジェクトと部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>プロジェクト名が「新製品」で始まるプロジェクトの部門名を教えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>プロジェクトと部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>各部門のプロジェクトの合計予算を計算してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>プロジェクトと部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>予算が最も高いプロジェクトの名前と部門名は何ですか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>プロジェクトと部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>営業部門のプロジェクトの平均予算を計算してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>プロジェクトと部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>プロジェクトの開始日が2025年3月以降のものを部門名とともにリストしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>プロジェクトと部門の組み合わせ</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>各部門のプロジェクト数を予算の降順で表示してください。</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Confidential- Oracle Internal</oddFooter>
-  </headerFooter>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{f3e58186-1c1b-4537-900b-8707ad116850}" enabled="1" method="Standard" siteId="{4e2c6054-71cb-48f1-bd6c-3a9705aca71b}" contentBits="2" removed="0"/>
-</clbl:labelList>
 </file>